--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_怪物技能效果配置表_Combat_MonsterSkillEffectConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_怪物技能效果配置表_Combat_MonsterSkillEffectConfig.xlsx
@@ -1068,6 +1068,9 @@
   <sheetPr/>
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="26.625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
